--- a/backend/tahsilat/src/main/resources/data/tahsilatlar.xlsx
+++ b/backend/tahsilat/src/main/resources/data/tahsilatlar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programs\tahsilat-app\backend\tahsilat\src\main\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FC2093-3D39-484F-8E6A-EBD0A25D6E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5876095F-73BE-41A0-81EF-B6DD6398755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,7 +1603,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9C3E96C0-D23A-420A-B5D1-47C548B77943}" name="Tablo13" displayName="Tablo13" ref="A1:F216" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:F216" xr:uid="{9C3E96C0-D23A-420A-B5D1-47C548B77943}"/>
+  <autoFilter ref="A1:F216" xr:uid="{9C3E96C0-D23A-420A-B5D1-47C548B77943}">
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F215">
     <sortCondition ref="A1:A216"/>
   </sortState>
@@ -1941,7 +1947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1958,7 +1964,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1975,7 +1981,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1998,7 +2004,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2020,7 +2026,7 @@
       <c r="H5" s="2"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2043,7 +2049,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2066,7 +2072,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2089,7 +2095,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2108,7 +2114,7 @@
       <c r="H9" s="2"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2130,7 +2136,7 @@
       <c r="H10" s="2"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2150,7 +2156,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2170,7 +2176,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2192,7 +2198,7 @@
       <c r="H13" s="2"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2211,7 +2217,7 @@
       <c r="H14" s="2"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2233,7 +2239,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2255,7 +2261,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2273,7 +2279,7 @@
       </c>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2294,7 +2300,7 @@
       </c>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2316,7 +2322,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2337,7 +2343,7 @@
       </c>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2358,7 +2364,7 @@
       </c>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2379,7 +2385,7 @@
       </c>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2397,7 +2403,7 @@
       </c>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2419,7 +2425,7 @@
       <c r="H24" s="2"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2441,7 +2447,7 @@
       <c r="H25" s="2"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2464,7 +2470,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2486,7 +2492,7 @@
       <c r="H27" s="2"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2508,7 +2514,7 @@
       <c r="H28" s="2"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2530,7 +2536,7 @@
       <c r="H29" s="2"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2549,7 +2555,7 @@
       <c r="H30" s="2"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2568,7 +2574,7 @@
       <c r="H31" s="2"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2590,7 +2596,7 @@
       <c r="H32" s="2"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2840,7 +2846,7 @@
       <c r="H45" s="2"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2859,7 +2865,7 @@
       <c r="H46" s="2"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2878,7 +2884,7 @@
       <c r="H47" s="2"/>
       <c r="K47" s="4"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2897,7 +2903,7 @@
       <c r="H48" s="2"/>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2916,7 +2922,7 @@
       <c r="H49" s="2"/>
       <c r="K49" s="4"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2938,7 +2944,7 @@
       <c r="H50" s="2"/>
       <c r="K50" s="4"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2960,7 +2966,7 @@
       <c r="H51" s="2"/>
       <c r="K51" s="4"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2982,7 +2988,7 @@
       <c r="H52" s="2"/>
       <c r="K52" s="4"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3004,7 +3010,7 @@
       <c r="H53" s="2"/>
       <c r="K53" s="4"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3026,7 +3032,7 @@
       <c r="H54" s="2"/>
       <c r="K54" s="4"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3045,7 +3051,7 @@
       <c r="H55" s="2"/>
       <c r="K55" s="4"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3064,7 +3070,7 @@
       <c r="H56" s="2"/>
       <c r="K56" s="4"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3083,7 +3089,7 @@
       <c r="H57" s="2"/>
       <c r="K57" s="4"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3105,7 +3111,7 @@
       <c r="H58" s="2"/>
       <c r="K58" s="4"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3127,7 +3133,7 @@
       <c r="H59" s="2"/>
       <c r="K59" s="4"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3149,7 +3155,7 @@
       <c r="H60" s="2"/>
       <c r="K60" s="4"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3168,7 +3174,7 @@
       <c r="H61" s="2"/>
       <c r="K61" s="4"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3187,7 +3193,7 @@
       <c r="H62" s="2"/>
       <c r="K62" s="4"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3209,7 +3215,7 @@
       <c r="H63" s="2"/>
       <c r="K63" s="4"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3231,7 +3237,7 @@
       <c r="H64" s="2"/>
       <c r="K64" s="4"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3250,7 +3256,7 @@
       <c r="H65" s="2"/>
       <c r="K65" s="4"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3269,7 +3275,7 @@
       <c r="H66" s="2"/>
       <c r="K66" s="4"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3288,7 +3294,7 @@
       <c r="H67" s="2"/>
       <c r="K67" s="4"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3307,7 +3313,7 @@
       <c r="H68" s="2"/>
       <c r="K68" s="4"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3326,7 +3332,7 @@
       <c r="H69" s="2"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3345,7 +3351,7 @@
       <c r="H70" s="2"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3364,7 +3370,7 @@
       <c r="H71" s="2"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3383,7 +3389,7 @@
       <c r="H72" s="2"/>
       <c r="K72" s="4"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3402,7 +3408,7 @@
       <c r="H73" s="2"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3421,7 +3427,7 @@
       <c r="H74" s="2"/>
       <c r="K74" s="4"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3443,7 +3449,7 @@
       <c r="H75" s="2"/>
       <c r="K75" s="4"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3465,7 +3471,7 @@
       <c r="H76" s="2"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3484,7 +3490,7 @@
       <c r="H77" s="2"/>
       <c r="K77" s="4"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3503,7 +3509,7 @@
       <c r="H78" s="2"/>
       <c r="K78" s="4"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3525,7 +3531,7 @@
       <c r="H79" s="2"/>
       <c r="K79" s="4"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3547,7 +3553,7 @@
       <c r="H80" s="2"/>
       <c r="K80" s="4"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3566,7 +3572,7 @@
       <c r="H81" s="2"/>
       <c r="K81" s="4"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3588,7 +3594,7 @@
       <c r="H82" s="2"/>
       <c r="K82" s="4"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3607,7 +3613,7 @@
       <c r="H83" s="2"/>
       <c r="K83" s="4"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3626,7 +3632,7 @@
       <c r="H84" s="2"/>
       <c r="K84" s="4"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3645,7 +3651,7 @@
       <c r="H85" s="2"/>
       <c r="K85" s="4"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3664,7 +3670,7 @@
       <c r="H86" s="2"/>
       <c r="K86" s="4"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3683,7 +3689,7 @@
       <c r="H87" s="2"/>
       <c r="K87" s="4"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3705,7 +3711,7 @@
       <c r="H88" s="2"/>
       <c r="K88" s="4"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3727,7 +3733,7 @@
       <c r="H89" s="2"/>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3749,7 +3755,7 @@
       <c r="H90" s="2"/>
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3771,7 +3777,7 @@
       <c r="H91" s="2"/>
       <c r="K91" s="4"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3793,7 +3799,7 @@
       <c r="H92" s="2"/>
       <c r="K92" s="4"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3815,7 +3821,7 @@
       <c r="H93" s="2"/>
       <c r="K93" s="4"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3834,7 +3840,7 @@
       <c r="H94" s="2"/>
       <c r="K94" s="4"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3853,7 +3859,7 @@
       <c r="H95" s="2"/>
       <c r="K95" s="4"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3872,7 +3878,7 @@
       <c r="H96" s="2"/>
       <c r="K96" s="4"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3891,7 +3897,7 @@
       <c r="H97" s="2"/>
       <c r="K97" s="4"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3910,7 +3916,7 @@
       <c r="H98" s="2"/>
       <c r="K98" s="4"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3929,7 +3935,7 @@
       <c r="H99" s="2"/>
       <c r="K99" s="4"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3948,7 +3954,7 @@
       <c r="H100" s="2"/>
       <c r="K100" s="4"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3967,7 +3973,7 @@
       <c r="H101" s="2"/>
       <c r="K101" s="4"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3986,7 +3992,7 @@
       <c r="H102" s="2"/>
       <c r="K102" s="4"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4008,7 +4014,7 @@
       <c r="H103" s="2"/>
       <c r="K103" s="4"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4027,7 +4033,7 @@
       <c r="H104" s="2"/>
       <c r="K104" s="4"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4046,7 +4052,7 @@
       <c r="H105" s="2"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4065,7 +4071,7 @@
       <c r="H106" s="2"/>
       <c r="K106" s="4"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4087,7 +4093,7 @@
       <c r="H107" s="2"/>
       <c r="K107" s="4"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -4109,7 +4115,7 @@
       <c r="H108" s="2"/>
       <c r="K108" s="4"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4131,7 +4137,7 @@
       <c r="H109" s="2"/>
       <c r="K109" s="4"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4153,7 +4159,7 @@
       <c r="H110" s="2"/>
       <c r="K110" s="4"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4175,7 +4181,7 @@
       <c r="H111" s="2"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4194,7 +4200,7 @@
       <c r="H112" s="2"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4213,7 +4219,7 @@
       <c r="H113" s="2"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4232,7 +4238,7 @@
       <c r="H114" s="2"/>
       <c r="K114" s="4"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4251,7 +4257,7 @@
       <c r="H115" s="2"/>
       <c r="K115" s="4"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4270,7 +4276,7 @@
       <c r="H116" s="2"/>
       <c r="K116" s="4"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4289,7 +4295,7 @@
       <c r="H117" s="2"/>
       <c r="K117" s="4"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4308,7 +4314,7 @@
       <c r="H118" s="2"/>
       <c r="K118" s="4"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -4327,7 +4333,7 @@
       <c r="H119" s="2"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4346,7 +4352,7 @@
       <c r="H120" s="2"/>
       <c r="K120" s="4"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4365,7 +4371,7 @@
       <c r="H121" s="2"/>
       <c r="K121" s="4"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4387,7 +4393,7 @@
       <c r="H122" s="2"/>
       <c r="K122" s="4"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4406,7 +4412,7 @@
       <c r="H123" s="2"/>
       <c r="K123" s="4"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4425,7 +4431,7 @@
       <c r="H124" s="2"/>
       <c r="K124" s="4"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4444,7 +4450,7 @@
       <c r="H125" s="2"/>
       <c r="K125" s="4"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4463,7 +4469,7 @@
       <c r="H126" s="2"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4482,7 +4488,7 @@
       <c r="H127" s="2"/>
       <c r="K127" s="4"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4501,7 +4507,7 @@
       <c r="H128" s="2"/>
       <c r="K128" s="4"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4520,7 +4526,7 @@
       <c r="H129" s="2"/>
       <c r="K129" s="4"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4539,7 +4545,7 @@
       <c r="H130" s="2"/>
       <c r="K130" s="4"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4558,7 +4564,7 @@
       <c r="H131" s="2"/>
       <c r="K131" s="4"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4577,7 +4583,7 @@
       <c r="H132" s="2"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4596,7 +4602,7 @@
       <c r="H133" s="2"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4615,7 +4621,7 @@
       <c r="H134" s="2"/>
       <c r="K134" s="4"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4637,7 +4643,7 @@
       <c r="H135" s="2"/>
       <c r="K135" s="4"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4656,7 +4662,7 @@
       <c r="H136" s="2"/>
       <c r="K136" s="4"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4675,7 +4681,7 @@
       <c r="H137" s="2"/>
       <c r="K137" s="4"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4694,7 +4700,7 @@
       <c r="H138" s="2"/>
       <c r="K138" s="4"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4713,7 +4719,7 @@
       <c r="H139" s="2"/>
       <c r="K139" s="4"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4732,7 +4738,7 @@
       <c r="H140" s="2"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4751,7 +4757,7 @@
       <c r="H141" s="2"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4770,7 +4776,7 @@
       <c r="H142" s="2"/>
       <c r="K142" s="4"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4789,7 +4795,7 @@
       <c r="H143" s="2"/>
       <c r="K143" s="4"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4808,7 +4814,7 @@
       <c r="H144" s="2"/>
       <c r="K144" s="4"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4827,7 +4833,7 @@
       <c r="H145" s="2"/>
       <c r="K145" s="4"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4846,7 +4852,7 @@
       <c r="H146" s="2"/>
       <c r="K146" s="4"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4865,7 +4871,7 @@
       <c r="H147" s="2"/>
       <c r="K147" s="4"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4884,7 +4890,7 @@
       <c r="H148" s="2"/>
       <c r="K148" s="4"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4903,7 +4909,7 @@
       <c r="H149" s="2"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4925,7 +4931,7 @@
       <c r="H150" s="2"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4947,7 +4953,7 @@
       <c r="H151" s="2"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4966,7 +4972,7 @@
       <c r="H152" s="2"/>
       <c r="K152" s="4"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4988,7 +4994,7 @@
       <c r="H153" s="2"/>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5007,7 +5013,7 @@
       <c r="H154" s="2"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5026,7 +5032,7 @@
       <c r="H155" s="2"/>
       <c r="K155" s="4"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5045,7 +5051,7 @@
       <c r="H156" s="2"/>
       <c r="K156" s="4"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5064,7 +5070,7 @@
       <c r="H157" s="2"/>
       <c r="K157" s="4"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5083,7 +5089,7 @@
       <c r="H158" s="2"/>
       <c r="K158" s="4"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5105,7 +5111,7 @@
       <c r="H159" s="2"/>
       <c r="K159" s="4"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5124,7 +5130,7 @@
       <c r="H160" s="2"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5146,7 +5152,7 @@
       <c r="H161" s="2"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5165,7 +5171,7 @@
       <c r="H162" s="2"/>
       <c r="K162" s="4"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5184,7 +5190,7 @@
       <c r="H163" s="2"/>
       <c r="K163" s="4"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5206,7 +5212,7 @@
       <c r="H164" s="2"/>
       <c r="K164" s="4"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5228,7 +5234,7 @@
       <c r="H165" s="2"/>
       <c r="K165" s="4"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5250,7 +5256,7 @@
       <c r="H166" s="2"/>
       <c r="K166" s="4"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5269,7 +5275,7 @@
       <c r="H167" s="2"/>
       <c r="K167" s="4"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5288,7 +5294,7 @@
       <c r="H168" s="2"/>
       <c r="K168" s="4"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5307,7 +5313,7 @@
       <c r="H169" s="2"/>
       <c r="K169" s="4"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5326,7 +5332,7 @@
       <c r="H170" s="2"/>
       <c r="K170" s="4"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -5345,7 +5351,7 @@
       <c r="H171" s="2"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5364,7 +5370,7 @@
       <c r="H172" s="2"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5383,7 +5389,7 @@
       <c r="H173" s="2"/>
       <c r="K173" s="4"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5402,7 +5408,7 @@
       <c r="H174" s="2"/>
       <c r="K174" s="4"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5424,7 +5430,7 @@
       <c r="H175" s="2"/>
       <c r="K175" s="4"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5446,7 +5452,7 @@
       <c r="H176" s="2"/>
       <c r="K176" s="4"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5465,7 +5471,7 @@
       <c r="H177" s="2"/>
       <c r="K177" s="4"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5484,7 +5490,7 @@
       <c r="H178" s="2"/>
       <c r="K178" s="4"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -5503,7 +5509,7 @@
       <c r="H179" s="2"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5525,7 +5531,7 @@
       <c r="H180" s="2"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5547,7 +5553,7 @@
       <c r="H181" s="2"/>
       <c r="K181" s="4"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5567,7 +5573,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5587,7 +5593,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -5604,7 +5610,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -5624,7 +5630,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -5644,7 +5650,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -5661,7 +5667,7 @@
         <v>4460</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5678,7 +5684,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -5695,7 +5701,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -5715,7 +5721,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -5735,7 +5741,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -5752,7 +5758,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -5789,7 +5795,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5809,7 +5815,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -5826,7 +5832,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -5911,7 +5917,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -5948,7 +5954,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -5968,7 +5974,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -5988,7 +5994,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6008,7 +6014,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6028,7 +6034,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6048,7 +6054,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6068,7 +6074,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6088,7 +6094,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6188,7 +6194,7 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
